--- a/input/images/tables/us_core_reqs.xlsx
+++ b/input/images/tables/us_core_reqs.xlsx
@@ -20222,13 +20222,17 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SHOULD</t>
+          <t>DEPRECATED</t>
         </is>
       </c>
       <c r="H218" t="n">
-        <v>3</v>
-      </c>
-      <c r="I218" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>promoted to a Common Clinical Note</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr">
         <is>
           <t>Server</t>
@@ -22924,15 +22928,12 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://hl7.org/fhir/us/core/STU8/medication-list.html#options-for-representing-medication, https://build.fhir.org/ig/HL7/US-Core/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, 
-https://build.fhir.org/ig/HL7/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://build.fhir.org/ig/HL7/US-Core/StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance
-</t>
+          <t>https://hl7.org/fhir/us/core/STU8/medication-list.html#options-for-representing-medication, https://build.fhir.org/ig/HL7/US-Core/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://build.fhir.org/ig/HL7/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://build.fhir.org/ig/HL7/US-Core/StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">medication-list.html#options-for-representing-medication, StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance
-</t>
+          <t>medication-list.html#options-for-representing-medication, StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medication.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -22968,19 +22969,17 @@
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr">
         <is>
-          <t>medication-list,StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medication</t>
+          <t>medication-list,StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medication,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t xml:space="preserve">options-for-representing-medication,profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance
-</t>
+          <t>options-for-representing-medication,profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medication-List: Options-For-Representing-Medication, Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medication: Profile-Specific-Implementation-Guidance
-</t>
+          <t>Medication-List: Options-For-Representing-Medication, Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medication: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V249" t="inlineStr"/>
@@ -24881,7 +24880,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Every Server that supports the USDCI Data Class “Health Status/Assessments”:
+          <t>Every Server that supports the USDCI Data Class “Health Status Assessments”:
 **SHALL** support representing clinical judgments using [US Core Condition Problems and Health Concerns Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-condition-problems-health-concerns.html) or [US Core Simple Observation Profile](https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-simple-observation.html).</t>
         </is>
       </c>
@@ -24975,7 +24974,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Every Server that supports the USDCI Data Class “Health Status/Assessments”:
+          <t>Every Server that supports the USDCI Data Class “Health Status Assessments”:
 ...
 The US Core Simple Observation Profile's Observation.derivedFrom element **SHOULD** reference the [Structured Screening and Assessment](https://hl7.org/fhir/us/core/STU8/screening-and-assessments.html#structured-screening-and-assessments) upon which clinical judgment observations are made</t>
         </is>
@@ -25073,7 +25072,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Every Server that supports the USDCI Data Class “Health Status/Assessments”:
+          <t>Every Server that supports the USDCI Data Class “Health Status Assessments”:
 ...
 the US Core Condition Profile's Condition.evidence.detail element **SHOULD** reference the [Structured Screening and Assessment](https://hl7.org/fhir/us/core/STU8/screening-and-assessments.html#structured-screening-and-assessments) which assist in diagnosing problems or health concerns.</t>
         </is>
@@ -36104,12 +36103,12 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -36145,17 +36144,17 @@
       <c r="R400" t="inlineStr"/>
       <c r="S400" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest</t>
+          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T400" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U400" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V400" t="inlineStr">
@@ -36185,12 +36184,12 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -36226,17 +36225,17 @@
       <c r="R401" t="inlineStr"/>
       <c r="S401" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest</t>
+          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T401" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U401" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V401" t="inlineStr">
@@ -36266,12 +36265,12 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -36311,17 +36310,17 @@
       <c r="R402" t="inlineStr"/>
       <c r="S402" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest</t>
+          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T402" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U402" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V402" t="inlineStr">
@@ -36359,12 +36358,12 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -36404,17 +36403,17 @@
       <c r="R403" t="inlineStr"/>
       <c r="S403" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest</t>
+          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T403" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U403" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V403" t="inlineStr">
@@ -36452,12 +36451,12 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -36493,17 +36492,17 @@
       <c r="R404" t="inlineStr"/>
       <c r="S404" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest</t>
+          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T404" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U404" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V404" t="inlineStr">
@@ -36537,12 +36536,12 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/STU8/StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, https://hl7.org/fhir/us/core/StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance</t>
+          <t>StructureDefinition-us-core-medicationdispense.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationrequest.html#profile-specific-implementation-guidance, StructureDefinition-us-core-medicationadministration.html#profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -36578,17 +36577,17 @@
       <c r="R405" t="inlineStr"/>
       <c r="S405" t="inlineStr">
         <is>
-          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest</t>
+          <t>StructureDefinition-us-core-medicationdispense,StructureDefinition-us-core-medicationrequest,StructureDefinition-us-core-medicationadministration</t>
         </is>
       </c>
       <c r="T405" t="inlineStr">
         <is>
-          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
+          <t>profile-specific-implementation-guidance,profile-specific-implementation-guidance,profile-specific-implementation-guidance</t>
         </is>
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance</t>
+          <t>Structuredefinition-Us-Core-Medicationdispense: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationrequest: Profile-Specific-Implementation-Guidance, Structuredefinition-Us-Core-Medicationadministration: Profile-Specific-Implementation-Guidance</t>
         </is>
       </c>
       <c r="V405" t="inlineStr">
@@ -54259,7 +54258,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Servers that support the USCDI Health Status/Assessments Data Class **SHALL** support the US Core Observation Screening Assessment Profile</t>
+          <t>Servers that support the USCDI Health Status Assessments Data Class **SHALL** support the US Core Observation Screening Assessment Profile</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -54289,7 +54288,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>Servers that support the USCDI Health Status/Assessments Data Class</t>
+          <t>Servers that support the USCDI Health Status Assessments Data Class</t>
         </is>
       </c>
       <c r="O608" t="inlineStr"/>
@@ -54352,7 +54351,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Servers that support the USCDI Health Status/Assessments Data Class ... **SHOULD** support the SDC Base Questionnaire and the US Core QuestionnaireResponse Profile."</t>
+          <t>Servers that support the USCDI Health Status Assessments Data Class ... **SHOULD** support the SDC Base Questionnaire and the US Core QuestionnaireResponse Profile."</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -54378,7 +54377,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>Servers that support the USCDI Health Status/Assessments Data Class</t>
+          <t>Servers that support the USCDI Health Status Assessments Data Class</t>
         </is>
       </c>
       <c r="O609" t="inlineStr"/>
@@ -57339,7 +57338,11 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr"/>
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="B645" t="n">
         <v>857</v>
       </c>
@@ -57360,7 +57363,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>For the USCDI *Laboratory Order*, *Imaging Order*, *Clinical Test Order*, and *Procedure Order* Data Elements, implementers **SHOULD** use the corresponding category codes listed in the table</t>
+          <t>For the USCDI *Laboratory Order*, *Imaging Order*, *Clinical Test Order*, *Procedure Order*, and *Referral Order* Data Elements, implementers **SHOULD** use the corresponding category codes listed in the table</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -62196,27 +62199,76 @@
       <c r="AE704" t="inlineStr"/>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr"/>
-      <c r="B705" t="inlineStr"/>
-      <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
-      <c r="E705" t="inlineStr"/>
-      <c r="F705" t="inlineStr"/>
-      <c r="G705" t="inlineStr"/>
-      <c r="H705" t="inlineStr"/>
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>917</v>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>CONF-0917</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/STU8/clinical-notes.html#clinical-notes</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>clinical-notes.html#clinical-notes</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Servers **SHALL** support, at minimum, these … "Common Clinical Notes":
+[Referral Note (57133-1)](https://loinc.org/57133-1.html)</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H705" t="n">
+        <v>1</v>
+      </c>
       <c r="I705" t="inlineStr"/>
-      <c r="J705" t="inlineStr"/>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
       <c r="K705" t="inlineStr"/>
       <c r="L705" t="inlineStr"/>
-      <c r="M705" t="inlineStr"/>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="N705" t="inlineStr"/>
       <c r="O705" t="inlineStr"/>
       <c r="P705" t="inlineStr"/>
       <c r="Q705" t="inlineStr"/>
       <c r="R705" t="inlineStr"/>
-      <c r="S705" t="inlineStr"/>
-      <c r="T705" t="inlineStr"/>
-      <c r="U705" t="inlineStr"/>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>clinical-notes</t>
+        </is>
+      </c>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>clinical-notes</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>Clinical-Notes: Clinical-Notes</t>
+        </is>
+      </c>
       <c r="V705" t="inlineStr"/>
       <c r="W705" t="inlineStr"/>
       <c r="X705" t="inlineStr"/>
@@ -62459,6 +62511,670 @@
       <c r="AD712" t="inlineStr"/>
       <c r="AE712" t="inlineStr"/>
     </row>
+    <row r="713">
+      <c r="A713" t="inlineStr"/>
+      <c r="B713" t="inlineStr"/>
+      <c r="C713" t="inlineStr"/>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr"/>
+      <c r="K713" t="inlineStr"/>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr"/>
+      <c r="N713" t="inlineStr"/>
+      <c r="O713" t="inlineStr"/>
+      <c r="P713" t="inlineStr"/>
+      <c r="Q713" t="inlineStr"/>
+      <c r="R713" t="inlineStr"/>
+      <c r="S713" t="inlineStr"/>
+      <c r="T713" t="inlineStr"/>
+      <c r="U713" t="inlineStr"/>
+      <c r="V713" t="inlineStr"/>
+      <c r="W713" t="inlineStr"/>
+      <c r="X713" t="inlineStr"/>
+      <c r="Y713" t="inlineStr"/>
+      <c r="Z713" t="inlineStr"/>
+      <c r="AA713" t="inlineStr"/>
+      <c r="AB713" t="inlineStr"/>
+      <c r="AC713" t="inlineStr"/>
+      <c r="AD713" t="inlineStr"/>
+      <c r="AE713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>918</v>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>CONF-0918</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/StructureDefinition-us-core-relatedperson.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-relatedperson.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>For the USCDI *Healthcare Agent* Data Element, systems **SHOULD** use the durable power of attorney code DPOWATT or the healthcare power of attorney code HPOWATT in `RelatedPerson.relationship`</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="H714" t="n">
+        <v>3</v>
+      </c>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr"/>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr"/>
+      <c r="O714" t="inlineStr"/>
+      <c r="P714" t="inlineStr"/>
+      <c r="Q714" t="inlineStr"/>
+      <c r="R714" t="inlineStr"/>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-relatedperson</t>
+        </is>
+      </c>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U714" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Relatedperson: Profile-Specific-Implementation-Guidance</t>
+        </is>
+      </c>
+      <c r="V714" t="inlineStr"/>
+      <c r="W714" t="inlineStr"/>
+      <c r="X714" t="inlineStr"/>
+      <c r="Y714" t="inlineStr"/>
+      <c r="Z714" t="inlineStr"/>
+      <c r="AA714" t="inlineStr"/>
+      <c r="AB714" t="inlineStr"/>
+      <c r="AC714" t="inlineStr"/>
+      <c r="AD714" t="inlineStr"/>
+      <c r="AE714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>919</v>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>CONF-0919</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/StructureDefinition-us-core-careteam.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-careteam.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>For the USCDI *Healthcare Agent* Data Element, systems **SHOULD** use the LOINC code 81335-2 (Patient Healthcare agent), the durable power of attorney code DPOWATT, or the healthcare power of attorney code HPOWATT in `CareTeam.participant.role`</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="H715" t="n">
+        <v>3</v>
+      </c>
+      <c r="I715" t="inlineStr"/>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr"/>
+      <c r="L715" t="inlineStr"/>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr"/>
+      <c r="O715" t="inlineStr"/>
+      <c r="P715" t="inlineStr"/>
+      <c r="Q715" t="inlineStr"/>
+      <c r="R715" t="inlineStr"/>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-careteam</t>
+        </is>
+      </c>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Careteam: Profile-Specific-Implementation-Guidance</t>
+        </is>
+      </c>
+      <c r="V715" t="inlineStr"/>
+      <c r="W715" t="inlineStr"/>
+      <c r="X715" t="inlineStr"/>
+      <c r="Y715" t="inlineStr"/>
+      <c r="Z715" t="inlineStr"/>
+      <c r="AA715" t="inlineStr"/>
+      <c r="AB715" t="inlineStr"/>
+      <c r="AC715" t="inlineStr"/>
+      <c r="AD715" t="inlineStr"/>
+      <c r="AE715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr"/>
+      <c r="B716" t="n">
+        <v>920</v>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>CONF-0920</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/StructureDefinition-us-core-procedure.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-procedure.html#profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Servers **SHALL** use the status code: not-done to represent that a procedure was not performed.</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>DEPRECATED</t>
+        </is>
+      </c>
+      <c r="H716" t="n">
+        <v>6</v>
+      </c>
+      <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr"/>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr"/>
+      <c r="O716" t="inlineStr"/>
+      <c r="P716" t="inlineStr"/>
+      <c r="Q716" t="inlineStr"/>
+      <c r="R716" t="inlineStr"/>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>StructureDefinition-us-core-procedure</t>
+        </is>
+      </c>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>profile-specific-implementation-guidance</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>Structuredefinition-Us-Core-Procedure: Profile-Specific-Implementation-Guidance</t>
+        </is>
+      </c>
+      <c r="V716" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="W716" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="X716" t="inlineStr"/>
+      <c r="Y716" t="inlineStr"/>
+      <c r="Z716" t="inlineStr"/>
+      <c r="AA716" t="inlineStr"/>
+      <c r="AB716" t="inlineStr"/>
+      <c r="AC716" t="inlineStr">
+        <is>
+          <t>ID retired in 10.0.0-ballot; the narrative statement was removed in favor of descriptive guidance</t>
+        </is>
+      </c>
+      <c r="AD716" t="inlineStr"/>
+      <c r="AE716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>921</v>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>CONF-0921</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>The following scopes that correspond directly to FHIR resource types **SHALL** be supported
+...
+[For] Appointment [the] &lt;patient|user|system&gt;/Appointment.rs [see [SMART Clinical Scope Syntax](https://hl7.org/fhir/smart-app-launch/STU2/scopes-and-launch-context.html#clinical-scope-syntax) for details on clinical data scopes]</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H717" t="n">
+        <v>1</v>
+      </c>
+      <c r="I717" t="inlineStr"/>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr"/>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>If Appointment is a supported resource type</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr"/>
+      <c r="P717" t="inlineStr"/>
+      <c r="Q717" t="inlineStr"/>
+      <c r="R717" t="inlineStr"/>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>scopes</t>
+        </is>
+      </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>Scopes: Scopes-For-Requesting-Fhir-Resources-By-Type</t>
+        </is>
+      </c>
+      <c r="V717" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="W717" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="X717" t="inlineStr"/>
+      <c r="Y717" t="inlineStr"/>
+      <c r="Z717" t="inlineStr"/>
+      <c r="AA717" t="inlineStr"/>
+      <c r="AB717" t="inlineStr"/>
+      <c r="AC717" t="inlineStr"/>
+      <c r="AD717" t="inlineStr"/>
+      <c r="AE717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>922</v>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>CONF-0922</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>The following scopes that correspond directly to FHIR resource types **SHALL** be supported
+...
+[For] MedicationAdministration [the] &lt;patient|user|system&gt;/MedicationAdministration.rs [see [SMART Clinical Scope Syntax](https://hl7.org/fhir/smart-app-launch/STU2/scopes-and-launch-context.html#clinical-scope-syntax) for details on clinical data scopes]</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H718" t="n">
+        <v>1</v>
+      </c>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr"/>
+      <c r="L718" t="inlineStr"/>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>If MedicationAdministration is a supported resource type</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr"/>
+      <c r="P718" t="inlineStr"/>
+      <c r="Q718" t="inlineStr"/>
+      <c r="R718" t="inlineStr"/>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>scopes</t>
+        </is>
+      </c>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>Scopes: Scopes-For-Requesting-Fhir-Resources-By-Type</t>
+        </is>
+      </c>
+      <c r="V718" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="W718" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="X718" t="inlineStr"/>
+      <c r="Y718" t="inlineStr"/>
+      <c r="Z718" t="inlineStr"/>
+      <c r="AA718" t="inlineStr"/>
+      <c r="AB718" t="inlineStr"/>
+      <c r="AC718" t="inlineStr"/>
+      <c r="AD718" t="inlineStr"/>
+      <c r="AE718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>923</v>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>CONF-0923</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>The following scopes that correspond directly to FHIR resource types **SHALL** be supported
+...
+[For] DeviceRequest [the] &lt;patient|user|system&gt;/DeviceRequest.rs [see [SMART Clinical Scope Syntax](https://hl7.org/fhir/smart-app-launch/STU2/scopes-and-launch-context.html#clinical-scope-syntax) for details on clinical data scopes]</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H719" t="n">
+        <v>1</v>
+      </c>
+      <c r="I719" t="inlineStr"/>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr"/>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>If DeviceRequest is a supported resource type</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr"/>
+      <c r="P719" t="inlineStr"/>
+      <c r="Q719" t="inlineStr"/>
+      <c r="R719" t="inlineStr"/>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>scopes</t>
+        </is>
+      </c>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>Scopes: Scopes-For-Requesting-Fhir-Resources-By-Type</t>
+        </is>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="W719" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="X719" t="inlineStr"/>
+      <c r="Y719" t="inlineStr"/>
+      <c r="Z719" t="inlineStr"/>
+      <c r="AA719" t="inlineStr"/>
+      <c r="AB719" t="inlineStr"/>
+      <c r="AC719" t="inlineStr"/>
+      <c r="AD719" t="inlineStr"/>
+      <c r="AE719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>924</v>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>CONF-0924</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>https://hl7.org/fhir/us/core/scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>scopes.html#scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>The following scopes that correspond directly to FHIR resource types **SHALL** be supported
+...
+[For] NutritionOrder [the] &lt;patient|user|system&gt;/NutritionOrder.rs [see [SMART Clinical Scope Syntax](https://hl7.org/fhir/smart-app-launch/STU2/scopes-and-launch-context.html#clinical-scope-syntax) for details on clinical data scopes]</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="H720" t="n">
+        <v>1</v>
+      </c>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr"/>
+      <c r="L720" t="inlineStr"/>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>If NutritionOrder is a supported resource type</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr"/>
+      <c r="P720" t="inlineStr"/>
+      <c r="Q720" t="inlineStr"/>
+      <c r="R720" t="inlineStr"/>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>scopes</t>
+        </is>
+      </c>
+      <c r="T720" t="inlineStr">
+        <is>
+          <t>scopes-for-requesting-fhir-resources-by-type</t>
+        </is>
+      </c>
+      <c r="U720" t="inlineStr">
+        <is>
+          <t>Scopes: Scopes-For-Requesting-Fhir-Resources-By-Type</t>
+        </is>
+      </c>
+      <c r="V720" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="W720" t="inlineStr">
+        <is>
+          <t>Server</t>
+        </is>
+      </c>
+      <c r="X720" t="inlineStr"/>
+      <c r="Y720" t="inlineStr"/>
+      <c r="Z720" t="inlineStr"/>
+      <c r="AA720" t="inlineStr"/>
+      <c r="AB720" t="inlineStr"/>
+      <c r="AC720" t="inlineStr"/>
+      <c r="AD720" t="inlineStr"/>
+      <c r="AE720" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
